--- a/AI_AuditLog_Example.xlsx
+++ b/AI_AuditLog_Example.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Desktop\SWR302\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DA664FF-BEDA-44C2-A590-BB561748CAAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCA7BAD5-E142-415A-838B-52745255105B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Metadata &amp; Summary" sheetId="1" r:id="rId1"/>
@@ -45,19 +45,10 @@
     <t>Student Name:</t>
   </si>
   <si>
-    <t>[Enter your name]</t>
-  </si>
-  <si>
     <t>Student ID:</t>
   </si>
   <si>
-    <t>[Enter your ID]</t>
-  </si>
-  <si>
     <t>Course:</t>
-  </si>
-  <si>
-    <t>[e.g., LAB211, PRF192, ADY201m]</t>
   </si>
   <si>
     <t>Assignment:</t>
@@ -511,6 +502,15 @@
   </si>
   <si>
     <t>Có, phần phân tích AC dễ bị bỏ sót tại mục 3b.</t>
+  </si>
+  <si>
+    <t>[Kiều Thị Kim Thoa]</t>
+  </si>
+  <si>
+    <t>[DE190363]</t>
+  </si>
+  <si>
+    <t>[SWR202]</t>
   </si>
 </sst>
 </file>
@@ -687,6 +687,9 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -702,9 +705,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1019,14 +1019,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
     </row>
     <row r="3" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -1038,138 +1038,138 @@
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>3</v>
+        <v>153</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>5</v>
+        <v>154</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>7</v>
+        <v>155</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C12" s="4" t="e">
         <f>C11/C10</f>
         <v>#VALUE!</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" s="6" t="s">
         <v>20</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D17" s="7" t="s">
         <v>24</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D18" s="7" t="s">
         <v>28</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
@@ -1177,62 +1177,62 @@
     </row>
     <row r="22" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B24" s="8">
         <v>0</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B25" s="8">
         <v>0</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="7" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B26" s="8">
         <v>0</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B27" s="8">
         <v>0</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -1258,131 +1258,131 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
+      <c r="A1" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
+      <c r="A2" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
     </row>
     <row r="3" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="D3" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="E3" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="F3" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="G3" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="H3" s="6" t="s">
         <v>51</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C4" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="F4" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="G4" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="H4" s="7" t="s">
         <v>123</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F5" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="H5" s="7" t="s">
         <v>133</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F6" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="H6" s="7" t="s">
         <v>134</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1605,68 +1605,68 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
-        <v>61</v>
-      </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
+      <c r="A1" s="23" t="s">
+        <v>58</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
+      <c r="A2" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
     </row>
     <row r="3" spans="1:6" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="D3" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="E3" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="F3" s="6" t="s">
         <v>65</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C4" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="F4" s="7" t="s">
         <v>139</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -1828,73 +1828,73 @@
     </row>
     <row r="30" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A34" s="7" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A35" s="7" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A36" s="7" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -1918,244 +1918,244 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
-        <v>88</v>
-      </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
+      <c r="A1" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="23" t="s">
-        <v>89</v>
-      </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
+      <c r="A2" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
     </row>
     <row r="4" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="D5" s="11" t="s">
         <v>91</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="12" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D6" s="13"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D7" s="13"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D8" s="13"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D9" s="13"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D10" s="13"/>
     </row>
     <row r="12" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D14" s="13"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="12" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D15" s="13"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D16" s="13"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="12" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D17" s="13"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="12" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D18" s="13"/>
     </row>
     <row r="20" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="14" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="15" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="15" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="16" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A27" s="17" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D28" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A29" s="9" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="72" x14ac:dyDescent="0.3">
@@ -2163,32 +2163,32 @@
         <v>3</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C30" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="D30" s="7" t="s">
         <v>151</v>
-      </c>
-      <c r="D30" s="7" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>148</v>
-      </c>
-      <c r="B31" s="24" t="s">
-        <v>149</v>
+        <v>145</v>
+      </c>
+      <c r="B31" s="18" t="s">
+        <v>146</v>
       </c>
       <c r="C31" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D31" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="D32" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
   </sheetData>
